--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488087_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488087_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7177</v>
+        <v>5.5355</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4891</v>
+        <v>3.8966</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2286</v>
+        <v>1.6389</v>
       </c>
       <c r="G2" t="n">
         <v>2.6377</v>
@@ -610,13 +610,13 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1316</v>
+        <v>-0.0506</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9873</v>
+        <v>-0.5798</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1189</v>
+        <v>0.5293</v>
       </c>
       <c r="V2" t="n">
         <v>2.552</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1236</v>
+        <v>5.134</v>
       </c>
       <c r="E3" t="n">
-        <v>2.436</v>
+        <v>2.3341</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6876</v>
+        <v>2.7999</v>
       </c>
       <c r="G3" t="n">
         <v>6.5218</v>
@@ -688,13 +688,13 @@
         <v>1.3876</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0206</v>
+        <v>-0.0102</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1834</v>
+        <v>-0.2853</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1628</v>
+        <v>0.2751</v>
       </c>
       <c r="V3" t="n">
         <v>0.2082</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1923</v>
+        <v>0.0623</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.0273</v>
+        <v>-1.1292</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2196</v>
+        <v>1.1915</v>
       </c>
       <c r="G4" t="n">
         <v>3.0113</v>
@@ -766,13 +766,13 @@
         <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0518</v>
+        <v>-0.1818</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.433</v>
+        <v>-0.5349</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3812</v>
+        <v>0.3531</v>
       </c>
       <c r="V4" t="n">
         <v>0.4044</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3495</v>
+        <v>-1.9744</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9726</v>
+        <v>-2.1763</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6231</v>
+        <v>0.2019</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4134</v>
@@ -844,13 +844,13 @@
         <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7982</v>
+        <v>0.1733</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.121</v>
+        <v>-0.3247</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9192</v>
+        <v>0.4981</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1397</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GUERRERO JONSSON</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8189</v>
+        <v>-2.0068</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4232</v>
+        <v>-0.8851</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3958</v>
+        <v>-1.1216</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1003</v>
+        <v>2.2099</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9612</v>
+        <v>1.3164</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8608</v>
+        <v>0.8935</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5784</v>
+        <v>1.6146</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6186</v>
+        <v>1.8362</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0402</v>
+        <v>-0.2216</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5219</v>
+        <v>0.5954</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3426</v>
+        <v>-0.5198</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8207</v>
+        <v>1.1151</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3876</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9455</v>
+        <v>-1.0086</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0696</v>
+        <v>-0.5174</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8759</v>
+        <v>-0.4912</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6145</v>
+        <v>-2.6134</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4074</v>
+        <v>-2.6134</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. CABRERA RUIZ</t>
+          <t>D. GUERRERO JONSSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6942</v>
+        <v>-2.0122</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0875</v>
+        <v>-1.7288</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6067</v>
+        <v>-0.2834</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1744</v>
+        <v>-1.1003</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0915</v>
+        <v>-1.9612</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.266</v>
+        <v>0.8608</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4635</v>
+        <v>-0.5784</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2156</v>
+        <v>-0.6186</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6791</v>
+        <v>0.0402</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2891</v>
+        <v>-0.5219</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1241</v>
+        <v>-1.3426</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4132</v>
+        <v>0.8207</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5947</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R7" t="n">
         <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9074</v>
+        <v>-1.1388</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.624</v>
+        <v>-0.3752</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2834</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2071</v>
+        <v>1.6145</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2071</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MOLPECERES ALCELAY</t>
+          <t>G. CABRERA RUIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.976</v>
+        <v>-2.48</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3404</v>
+        <v>-0.9856</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-1.4944</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3029</v>
+        <v>-0.1744</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4936</v>
+        <v>0.0915</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8093</v>
+        <v>-0.266</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9749</v>
+        <v>-0.4635</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2958</v>
+        <v>0.2156</v>
       </c>
       <c r="L8" t="n">
         <v>-0.6791</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.328</v>
+        <v>0.2891</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1979</v>
+        <v>-0.1241</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1301</v>
+        <v>0.4132</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1982</v>
+        <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8802</v>
+        <v>-1.6932</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3744</v>
+        <v>-0.5221</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5059</v>
+        <v>-1.1711</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>M. MOLPECERES ALCELAY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0601</v>
+        <v>-2.818</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2926</v>
+        <v>-2.2385</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7674</v>
+        <v>-0.5795</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2099</v>
+        <v>-1.3029</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3164</v>
+        <v>-0.4936</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8935</v>
+        <v>-0.8093</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6146</v>
+        <v>-0.9749</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8362</v>
+        <v>-0.2958</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2216</v>
+        <v>-0.6791</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5954</v>
+        <v>-0.328</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5198</v>
+        <v>-0.1979</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1151</v>
+        <v>-0.1301</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5947</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3876</v>
+        <v>0.1982</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0619</v>
+        <v>-0.7222</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.2725</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.137</v>
+        <v>-0.4497</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.6134</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.6134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2915</v>
+        <v>-3.7271</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.902</v>
+        <v>-1.3094</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3895</v>
+        <v>-2.4176</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9446</v>
@@ -1234,13 +1234,13 @@
         <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0209</v>
+        <v>-1.4564</v>
       </c>
       <c r="T10" t="n">
-        <v>0.18</v>
+        <v>-0.2275</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2008</v>
+        <v>-1.2289</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5331</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9151</v>
+        <v>-4.8132</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4079</v>
+        <v>-3.3061</v>
       </c>
       <c r="F11" t="n">
         <v>-1.5072</v>
@@ -1312,10 +1312,10 @@
         <v>0.5947</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9933</v>
+        <v>-1.8914</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8112</v>
+        <v>-0.7093</v>
       </c>
       <c r="U11" t="n">
         <v>-1.1821</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3262</v>
+        <v>-5.2981</v>
       </c>
       <c r="E12" t="n">
         <v>-1.5789</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7473</v>
+        <v>-3.7192</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0732</v>
@@ -1390,13 +1390,13 @@
         <v>0.3964</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.244</v>
+        <v>-1.216</v>
       </c>
       <c r="T12" t="n">
         <v>-0.312</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9321</v>
+        <v>-0.904</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4142</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.3979</v>
+        <v>-14.398</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.107299999999999</v>
+        <v>-9.107199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.2906</v>
+        <v>-5.290699999999999</v>
       </c>
       <c r="G13" t="n">
         <v>7.837600000000002</v>
@@ -1468,13 +1468,13 @@
         <v>9.911299999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.1958</v>
+        <v>-9.1959</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.6608</v>
+        <v>-4.6607</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.5351</v>
+        <v>-4.535</v>
       </c>
       <c r="V13" t="n">
         <v>-3.1284</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.4582</v>
+        <v>11.0893</v>
       </c>
       <c r="E14" t="n">
-        <v>9.0817</v>
+        <v>8.5724</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3765</v>
+        <v>2.5169</v>
       </c>
       <c r="G14" t="n">
         <v>6.0652</v>
@@ -1546,13 +1546,13 @@
         <v>2.5769</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5495</v>
+        <v>2.1805</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2394</v>
+        <v>1.7301</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3101</v>
+        <v>0.4505</v>
       </c>
       <c r="V14" t="n">
         <v>0.2666</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. MELERO ZURITA</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6529</v>
+        <v>3.6819</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3224</v>
+        <v>0.5131</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6695</v>
+        <v>3.1688</v>
       </c>
       <c r="G15" t="n">
-        <v>0.27</v>
+        <v>3.0183</v>
       </c>
       <c r="H15" t="n">
-        <v>0.842</v>
+        <v>2.2894</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5721000000000001</v>
+        <v>0.7289</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6517</v>
+        <v>3.1249</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5675</v>
+        <v>3.0808</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0842</v>
+        <v>0.0441</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3818</v>
+        <v>-0.1066</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7255</v>
+        <v>-0.7914</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6563</v>
+        <v>0.6848</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9911</v>
+        <v>-4.1627</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9822</v>
+        <v>2.1805</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5327</v>
+        <v>0.8351</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5955</v>
+        <v>0.0772</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.06279999999999999</v>
+        <v>0.7579</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1408</v>
+        <v>1.8107</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0663</v>
+        <v>1.4737</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2071</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>P. TRUÑO SOMS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8108</v>
+        <v>2.716</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3018</v>
+        <v>2.716</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1126</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0183</v>
+        <v>2.716</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2894</v>
+        <v>0.908</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7289</v>
+        <v>1.808</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1249</v>
+        <v>2.716</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0808</v>
+        <v>0.908</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0441</v>
+        <v>1.808</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1066</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7914</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6848</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.1627</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.036</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7377</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7017</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. TRUÑO SOMS</t>
+          <t>D. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.716</v>
+        <v>2.6153</v>
       </c>
       <c r="E17" t="n">
-        <v>2.716</v>
+        <v>2.8963</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0.281</v>
       </c>
       <c r="G17" t="n">
-        <v>2.716</v>
+        <v>0.27</v>
       </c>
       <c r="H17" t="n">
-        <v>0.908</v>
+        <v>0.842</v>
       </c>
       <c r="I17" t="n">
-        <v>1.808</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>2.716</v>
+        <v>1.6517</v>
       </c>
       <c r="K17" t="n">
-        <v>0.908</v>
+        <v>1.5675</v>
       </c>
       <c r="L17" t="n">
-        <v>1.808</v>
+        <v>0.0842</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.3818</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.7255</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.6563</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.495</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.1693</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.3257</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.1408</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0663</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>P. ÁVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6422</v>
+        <v>0.9053</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5006</v>
+        <v>0.9053</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1417</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2624</v>
+        <v>0.9053</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.7559</v>
+        <v>0.3027</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4935</v>
+        <v>0.6027</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5466</v>
+        <v>0.9053</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6269</v>
+        <v>0.3027</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0804</v>
+        <v>0.6027</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7158</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.129</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4132</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.0612</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9788</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0824</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ÁVALOS ORTIZ</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9053</v>
+        <v>0.2259</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9053</v>
+        <v>0.9416</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0.7157</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9053</v>
+        <v>-2.8593</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3027</v>
+        <v>-2.1994</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6027</v>
+        <v>-0.6599</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9053</v>
+        <v>-1.0005</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3027</v>
+        <v>-0.3292</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6027</v>
+        <v>-0.6713</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.8588</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-1.8702</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.3707</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.7386</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.3679</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.6808</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0033</v>
+        <v>0.1109</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9863</v>
+        <v>-0.7219</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.983</v>
+        <v>0.8328</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0955</v>
+        <v>-2.2624</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0404</v>
+        <v>-2.7559</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1358</v>
+        <v>0.4935</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2894</v>
+        <v>-1.5466</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2894</v>
+        <v>-1.6269</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.0804</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1939</v>
+        <v>-0.7158</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3298</v>
+        <v>-1.129</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1358</v>
+        <v>0.4132</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1982</v>
+        <v>1.784</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.1982</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3964</v>
+        <v>1.9822</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2904</v>
+        <v>1.5299</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.312</v>
+        <v>0.7564</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0216</v>
+        <v>0.7735</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="X20" t="n">
         <v>-1.2071</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6158</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4323</v>
+        <v>-0.4907</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0481</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8593</v>
+        <v>-1.3782</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1994</v>
+        <v>0.6535</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6599</v>
+        <v>-2.0317</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0005</v>
+        <v>-0.9882</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3292</v>
+        <v>1.0492</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6713</v>
+        <v>-2.0374</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8588</v>
+        <v>-0.39</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8702</v>
+        <v>-0.3957</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0114</v>
+        <v>0.0057</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9822</v>
+        <v>0.5947</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9822</v>
+        <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2124</v>
+        <v>0.8718</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2479</v>
+        <v>0.4975</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0355</v>
+        <v>0.3744</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.6808</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.0248</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1019</v>
+        <v>0.9863</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3544</v>
+        <v>-1.0111</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3782</v>
+        <v>0.0955</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6535</v>
+        <v>-0.0404</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0317</v>
+        <v>0.1358</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9882</v>
+        <v>0.2894</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0492</v>
+        <v>0.2894</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.0374</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.39</v>
+        <v>-0.1939</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3957</v>
+        <v>-0.3298</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0057</v>
+        <v>0.1358</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="S22" t="n">
-        <v>0.036</v>
+        <v>-0.3184</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1138</v>
+        <v>-0.312</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1498</v>
+        <v>-0.0065</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8207</v>
+        <v>-0.3042</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5285</v>
+        <v>-1.8154</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7077</v>
+        <v>1.5112</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6388</v>
@@ -2248,13 +2248,13 @@
         <v>1.9822</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0341</v>
+        <v>0.5506</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6753</v>
+        <v>0.0377</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7094</v>
+        <v>0.5129</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3277</v>
+        <v>-1.028</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1448</v>
+        <v>-2.7035</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1829</v>
+        <v>1.6754</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.1778</v>
+        <v>-2.3079</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0379</v>
+        <v>-1.1772</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.1398</v>
+        <v>-1.1307</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.1995</v>
+        <v>-1.7956</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1482</v>
+        <v>-0.5177</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.3477</v>
+        <v>-1.2779</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9782</v>
+        <v>-0.5123</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1861</v>
+        <v>-0.6595</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7922</v>
+        <v>0.1472</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1805</v>
+        <v>1.5858</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2664</v>
+        <v>0.826</v>
       </c>
       <c r="T24" t="n">
-        <v>1.2373</v>
+        <v>0.2241</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0291</v>
+        <v>0.6019</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.4074</v>
+        <v>-0.1408</v>
       </c>
       <c r="W24" t="n">
-        <v>2.0068</v>
+        <v>-0.1408</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.3467</v>
+        <v>-2.1505</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1109</v>
+        <v>-1.6541</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7642</v>
+        <v>-0.4963</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.3079</v>
+        <v>-4.1778</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.1772</v>
+        <v>-0.0379</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.1307</v>
+        <v>-4.1398</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.7956</v>
+        <v>-3.1995</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5177</v>
+        <v>0.1482</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.2779</v>
+        <v>-3.3477</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5123</v>
+        <v>-0.9782</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6595</v>
+        <v>-0.1861</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1472</v>
+        <v>-0.7922</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5073</v>
+        <v>1.4436</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1834</v>
+        <v>0.7279</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6907</v>
+        <v>0.7157</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1408</v>
+        <v>-0.4074</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1408</v>
+        <v>2.0068</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.9325</v>
+        <v>-2.8485</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.466</v>
+        <v>-4.8548</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5335</v>
+        <v>2.0063</v>
       </c>
       <c r="G26" t="n">
         <v>-5.2835</v>
@@ -2482,13 +2482,13 @@
         <v>2.3787</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2525</v>
+        <v>0.8315</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2458</v>
+        <v>0.3654</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0067</v>
+        <v>0.4661</v>
       </c>
       <c r="V26" t="n">
         <v>1.2071</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>14.3978</v>
+        <v>15.077</v>
       </c>
       <c r="E27" t="n">
-        <v>5.290699999999998</v>
+        <v>5.2906</v>
       </c>
       <c r="F27" t="n">
-        <v>9.107099999999999</v>
+        <v>9.7864</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.837599999999999</v>
+        <v>-7.837599999999998</v>
       </c>
       <c r="H27" t="n">
         <v>1.048</v>
@@ -2533,10 +2533,10 @@
         <v>-8.8857</v>
       </c>
       <c r="J27" t="n">
-        <v>0.632699999999998</v>
+        <v>0.6327000000000016</v>
       </c>
       <c r="K27" t="n">
-        <v>7.623599999999999</v>
+        <v>7.6236</v>
       </c>
       <c r="L27" t="n">
         <v>-6.990700000000001</v>
@@ -2560,13 +2560,13 @@
         <v>19.8223</v>
       </c>
       <c r="S27" t="n">
-        <v>9.1959</v>
+        <v>9.8749</v>
       </c>
       <c r="T27" t="n">
-        <v>4.535099999999999</v>
+        <v>4.535</v>
       </c>
       <c r="U27" t="n">
-        <v>4.660799999999999</v>
+        <v>5.34</v>
       </c>
       <c r="V27" t="n">
         <v>3.1286</v>
